--- a/ref_sim/openFAST_config_dyn_inflow.xlsx
+++ b/ref_sim/openFAST_config_dyn_inflow.xlsx
@@ -29,7 +29,7 @@
     <t xml:space="preserve">MainInput</t>
   </si>
   <si>
-    <t xml:space="preserve">../5MW_Baseline/5MW_Land_DLL_MPC.fst</t>
+    <t xml:space="preserve">../5MW_Baseline/5MW_Land_DLL_WTurb.fst</t>
   </si>
   <si>
     <t xml:space="preserve">ElastoDyn</t>
